--- a/doc/assets/02 Dommel opdrachten.xlsx
+++ b/doc/assets/02 Dommel opdrachten.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Beekvliet\2022-2023\Wiskunde\Klas 2c\Materiaal\Dommelproject\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Beekvliet\2024-2025\Diversen\Projectweek Dommel\Excelbestanden\Originelen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A44151DC-179C-421E-B41D-3583AE492FA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A3B245-22E1-4F8B-81A1-A39B417523B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F3D81243-57C0-487B-9D40-563A54D81D76}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F3D81243-57C0-487B-9D40-563A54D81D76}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdracht 2" sheetId="1" r:id="rId1"/>
@@ -376,9 +376,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Kantoorthema">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Thema">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -416,7 +416,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -522,7 +522,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -664,7 +664,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -769,7 +769,7 @@
   <dimension ref="A1:B53"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1370,6 +1370,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010047264B763F990948B4D334C39BBB59FB" ma:contentTypeVersion="2" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="aebce7bc0787a1224963e3dd86de1323">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ad94bf201bbfb35981ffb694a7753387">
     <xsd:element name="properties">
@@ -1483,29 +1498,35 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50441E63-484B-46A6-BEF5-883BC7C22DD9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CC436D-5654-4CFA-98A0-0BAFC136BC4F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958DDF26-89B5-433F-AB64-BE0A073B9C82}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958DDF26-89B5-433F-AB64-BE0A073B9C82}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CC436D-5654-4CFA-98A0-0BAFC136BC4F}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50441E63-484B-46A6-BEF5-883BC7C22DD9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/doc/assets/02 Dommel opdrachten.xlsx
+++ b/doc/assets/02 Dommel opdrachten.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A3B245-22E1-4F8B-81A1-A39B417523B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{F3D81243-57C0-487B-9D40-563A54D81D76}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F3D81243-57C0-487B-9D40-563A54D81D76}"/>
   </bookViews>
   <sheets>
     <sheet name="Opdracht 2" sheetId="1" r:id="rId1"/>
@@ -1370,18 +1370,18 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1499,18 +1499,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CC436D-5654-4CFA-98A0-0BAFC136BC4F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958DDF26-89B5-433F-AB64-BE0A073B9C82}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958DDF26-89B5-433F-AB64-BE0A073B9C82}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CC436D-5654-4CFA-98A0-0BAFC136BC4F}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/doc/assets/02 Dommel opdrachten.xlsx
+++ b/doc/assets/02 Dommel opdrachten.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Beekvliet\2024-2025\Diversen\Projectweek Dommel\Excelbestanden\Originelen\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A3B245-22E1-4F8B-81A1-A39B417523B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FD3412B-5A21-4296-A6CB-BB3AF079199F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{F3D81243-57C0-487B-9D40-563A54D81D76}"/>
   </bookViews>
   <sheets>
-    <sheet name="Opdracht 2" sheetId="1" r:id="rId1"/>
-    <sheet name="Opdracht 3" sheetId="2" r:id="rId2"/>
-    <sheet name="Opdracht 4" sheetId="3" r:id="rId3"/>
+    <sheet name="Stroomsnelheid" sheetId="1" r:id="rId1"/>
+    <sheet name="Kanoën" sheetId="2" r:id="rId2"/>
+    <sheet name="Waterschapsverkiezingen" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1379,12 +1379,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010047264B763F990948B4D334C39BBB59FB" ma:contentTypeVersion="2" ma:contentTypeDescription="Een nieuw document maken." ma:contentTypeScope="" ma:versionID="aebce7bc0787a1224963e3dd86de1323">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ad94bf201bbfb35981ffb694a7753387">
     <xsd:element name="properties">
@@ -1498,6 +1492,12 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{958DDF26-89B5-433F-AB64-BE0A073B9C82}">
   <ds:schemaRefs>
@@ -1507,15 +1507,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CC436D-5654-4CFA-98A0-0BAFC136BC4F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{50441E63-484B-46A6-BEF5-883BC7C22DD9}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1529,4 +1520,13 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55CC436D-5654-4CFA-98A0-0BAFC136BC4F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>